--- a/2026-04/R8コミュニティ活動推進交付金提出書類書式/【計画】①コミュニティ活動推進交付金申請書komikoufukinshinseisyo.xlsx
+++ b/2026-04/R8コミュニティ活動推進交付金提出書類書式/【計画】①コミュニティ活動推進交付金申請書komikoufukinshinseisyo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\jack\v3_fsroot\FS\地域コミュニティ支援課共有\【共有】地域コミュニティ係\67_町内会\04_コミュニティ活動推進交付金\R07\01【R7申請】（青少年含む）\HP更新用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyWorks\komatest\2026-04\R8コミュニティ活動推進交付金提出書類書式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1E48AE9-4A4C-4C25-9007-5A2818CC9770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F892782-EC6C-4F44-AADB-0B52D7CBA47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC6D069D-72C4-4D5A-9AC4-D32870AC9879}"/>
+    <workbookView xWindow="15972" yWindow="5556" windowWidth="19380" windowHeight="13752" xr2:uid="{AC6D069D-72C4-4D5A-9AC4-D32870AC9879}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,56 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
-  <si>
-    <t>令　和　 　年　度　（ 　　　　年度）　補　助　金　等　交　付　申　請　書</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>トシ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ホ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>スケ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>キン</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ナド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>コウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>サル</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>　（あて先）　横　須　賀　市　長</t>
     <rPh sb="4" eb="5">
@@ -221,16 +172,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>金　                円　</t>
-    <rPh sb="0" eb="1">
-      <t>キン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>世帯数</t>
     <rPh sb="0" eb="3">
       <t>セタイスウ</t>
@@ -238,13 +179,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　世帯　　　</t>
-    <rPh sb="1" eb="3">
-      <t>セタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>内訳</t>
     <rPh sb="0" eb="2">
       <t>ウチワケ</t>
@@ -301,6 +235,129 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>令　和　 ８年　度　（ 2026年度）　補　助　金　等　交　付　申　請　書</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>スケ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>サル</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駒寄町内会</t>
+    <rPh sb="0" eb="2">
+      <t>コマヨセ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チョウナイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>船越町６－１７－６６</t>
+    <rPh sb="0" eb="3">
+      <t>フナコシチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爲廣　哲朗</t>
+    <rPh sb="0" eb="2">
+      <t>タメヒロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テツロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>８６１－１６５７</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>均等割：</t>
+    <rPh sb="0" eb="3">
+      <t>キントウワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>101～300世帯では、204,000円</t>
+    <rPh sb="7" eb="9">
+      <t>セタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世帯割：</t>
+    <rPh sb="0" eb="2">
+      <t>セタイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（申請）世帯数×500円</t>
+    <rPh sb="1" eb="3">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>セタイスウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>エン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -309,7 +366,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;金&quot;\ #,##0\ &quot;円  &quot;"/>
+    <numFmt numFmtId="178" formatCode="General\ &quot;世帯  &quot;"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +410,14 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,7 +427,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -517,22 +587,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -581,7 +642,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -602,13 +675,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,9 +711,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -669,7 +751,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -775,7 +857,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -917,7 +999,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -925,10 +1007,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB11C9F-27F3-4103-8001-900EB463383F}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -936,21 +1022,21 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-    </row>
-    <row r="4" spans="1:9" ht="9.75" customHeight="1" thickBot="1"/>
-    <row r="5" spans="1:9">
+    <row r="3" spans="1:9" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -961,9 +1047,9 @@
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -974,7 +1060,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -985,7 +1071,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="8"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -996,20 +1082,22 @@
       <c r="H8" s="7"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="16" t="s">
+        <v>19</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1020,22 +1108,24 @@
       <c r="H10" s="7"/>
       <c r="I10" s="8"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>4</v>
-      </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="16" t="s">
+        <v>20</v>
+      </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="8"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1046,20 +1136,22 @@
       <c r="H12" s="7"/>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1070,20 +1162,22 @@
       <c r="H14" s="7"/>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="G15" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="H15" s="9"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1094,67 +1188,68 @@
       <c r="H16" s="7"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20" t="s">
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="26"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="18" t="s">
+      <c r="B18" s="23"/>
+      <c r="C18" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="26"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="18" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="27">
+        <f>SUM(E23:E25)</f>
+        <v>331000</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="B20" s="23"/>
+      <c r="C20" s="30">
+        <v>230</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1165,10 +1260,10 @@
       <c r="H21" s="7"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -1178,52 +1273,73 @@
       <c r="H22" s="7"/>
       <c r="I22" s="8"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="20">
+        <v>204000</v>
+      </c>
       <c r="F23" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
+      <c r="E24" s="18">
+        <f>C20*500</f>
+        <v>115000</v>
+      </c>
       <c r="F24" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="16" t="s">
-        <v>17</v>
+      <c r="C25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="18">
+        <v>12000</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1234,7 +1350,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="8"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1245,7 +1361,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="8"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1256,7 +1372,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1267,7 +1383,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="19.5" thickBot="1">
+    <row r="30" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1278,7 +1394,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="14"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -1289,9 +1405,9 @@
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" s="15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -1302,7 +1418,7 @@
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="15"/>
     </row>
   </sheetData>
